--- a/Excel/5. Logical/logical.xlsx
+++ b/Excel/5. Logical/logical.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Advance_Excel_BI\5. Logical\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DC_DDS_04\Excel\5. Logical\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{199F3840-01A7-4471-AF80-8219928A9B30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C688BFD1-8267-4986-A49F-32A5AFECBB5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" tabRatio="862" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -198,7 +198,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
@@ -317,7 +317,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -339,6 +339,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -486,7 +492,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="67">
+  <cellXfs count="66">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -564,6 +570,11 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -648,19 +659,15 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
+    <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{5985EC07-BD67-472F-A897-7B4FF2587B8F}"/>
+  </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -1534,10 +1541,10 @@
   <sheetData>
     <row r="1" spans="1:28" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1"/>
-      <c r="B1" s="35" t="s">
+      <c r="B1" s="38" t="s">
         <v>13</v>
       </c>
-      <c r="C1" s="35"/>
+      <c r="C1" s="38"/>
       <c r="D1" s="1"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
@@ -1545,25 +1552,25 @@
       <c r="H1" s="2"/>
       <c r="I1" s="8"/>
       <c r="J1" s="16"/>
-      <c r="K1" s="35" t="s">
+      <c r="K1" s="38" t="s">
         <v>0</v>
       </c>
-      <c r="L1" s="35"/>
-      <c r="M1" s="35"/>
-      <c r="N1" s="35"/>
-      <c r="O1" s="35"/>
-      <c r="P1" s="35"/>
+      <c r="L1" s="38"/>
+      <c r="M1" s="38"/>
+      <c r="N1" s="38"/>
+      <c r="O1" s="38"/>
+      <c r="P1" s="38"/>
       <c r="Q1" s="15"/>
-      <c r="R1" s="35"/>
-      <c r="S1" s="35"/>
-      <c r="T1" s="35"/>
-      <c r="U1" s="35"/>
-      <c r="V1" s="35"/>
-      <c r="W1" s="35"/>
-      <c r="X1" s="35"/>
-      <c r="Y1" s="35"/>
-      <c r="Z1" s="35"/>
-      <c r="AA1" s="35"/>
+      <c r="R1" s="38"/>
+      <c r="S1" s="38"/>
+      <c r="T1" s="38"/>
+      <c r="U1" s="38"/>
+      <c r="V1" s="38"/>
+      <c r="W1" s="38"/>
+      <c r="X1" s="38"/>
+      <c r="Y1" s="38"/>
+      <c r="Z1" s="38"/>
+      <c r="AA1" s="38"/>
       <c r="AB1" s="15"/>
     </row>
     <row r="2" spans="1:28" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.3"/>
@@ -1572,7 +1579,7 @@
       <c r="P3" s="27" t="s">
         <v>33</v>
       </c>
-      <c r="Q3" s="65" t="s">
+      <c r="Q3" s="35" t="s">
         <v>34</v>
       </c>
       <c r="R3" s="27" t="s">
@@ -1581,13 +1588,13 @@
     </row>
     <row r="4" spans="1:28" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="14"/>
-      <c r="C4" s="36" t="s">
+      <c r="C4" s="39" t="s">
         <v>6</v>
       </c>
-      <c r="D4" s="37"/>
-      <c r="E4" s="37"/>
-      <c r="F4" s="37"/>
-      <c r="G4" s="38"/>
+      <c r="D4" s="40"/>
+      <c r="E4" s="40"/>
+      <c r="F4" s="40"/>
+      <c r="G4" s="41"/>
       <c r="H4" s="14"/>
       <c r="I4" s="10"/>
       <c r="J4" s="18"/>
@@ -1616,11 +1623,11 @@
     </row>
     <row r="5" spans="1:28" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="3"/>
-      <c r="C5" s="39"/>
-      <c r="D5" s="40"/>
-      <c r="E5" s="40"/>
-      <c r="F5" s="40"/>
-      <c r="G5" s="41"/>
+      <c r="C5" s="42"/>
+      <c r="D5" s="43"/>
+      <c r="E5" s="43"/>
+      <c r="F5" s="43"/>
+      <c r="G5" s="44"/>
       <c r="H5" s="3"/>
       <c r="I5" s="11"/>
       <c r="J5" s="19"/>
@@ -1637,25 +1644,25 @@
       <c r="O5" s="24">
         <v>85</v>
       </c>
-      <c r="P5" s="63" t="b">
+      <c r="P5" s="24" t="b">
         <f>M5=100</f>
         <v>0</v>
       </c>
-      <c r="Q5" s="64" t="b">
+      <c r="Q5" s="37" t="b">
         <f>AND(M5&gt;75,N5&gt;75,O5&gt;75)</f>
         <v>1</v>
       </c>
-      <c r="R5" s="63" t="b">
+      <c r="R5" s="24" t="b">
         <f>OR(M5&lt;35,N5&lt;35,O5&lt;35)</f>
         <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:28" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C6" s="39"/>
-      <c r="D6" s="40"/>
-      <c r="E6" s="40"/>
-      <c r="F6" s="40"/>
-      <c r="G6" s="41"/>
+      <c r="C6" s="42"/>
+      <c r="D6" s="43"/>
+      <c r="E6" s="43"/>
+      <c r="F6" s="43"/>
+      <c r="G6" s="44"/>
       <c r="L6" s="24" t="s">
         <v>18</v>
       </c>
@@ -1668,25 +1675,25 @@
       <c r="O6" s="24">
         <v>43</v>
       </c>
-      <c r="P6" s="63" t="b">
+      <c r="P6" s="24" t="b">
         <f t="shared" ref="P6:P9" si="0">M6=100</f>
         <v>0</v>
       </c>
-      <c r="Q6" s="63" t="b">
+      <c r="Q6" s="24" t="b">
         <f t="shared" ref="Q6:Q9" si="1">AND(M6&gt;75,N6&gt;75,O6&gt;75)</f>
         <v>0</v>
       </c>
-      <c r="R6" s="63" t="b">
+      <c r="R6" s="24" t="b">
         <f t="shared" ref="R6:R9" si="2">OR(M6&lt;35,N6&lt;35,O6&lt;35)</f>
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:28" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C7" s="39"/>
-      <c r="D7" s="40"/>
-      <c r="E7" s="40"/>
-      <c r="F7" s="40"/>
-      <c r="G7" s="41"/>
+      <c r="C7" s="42"/>
+      <c r="D7" s="43"/>
+      <c r="E7" s="43"/>
+      <c r="F7" s="43"/>
+      <c r="G7" s="44"/>
       <c r="L7" s="24" t="s">
         <v>19</v>
       </c>
@@ -1699,25 +1706,25 @@
       <c r="O7" s="24">
         <v>79</v>
       </c>
-      <c r="P7" s="63" t="b">
+      <c r="P7" s="24" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Q7" s="64" t="b">
+      <c r="Q7" s="37" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="R7" s="63" t="b">
+      <c r="R7" s="24" t="b">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:28" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C8" s="39"/>
-      <c r="D8" s="40"/>
-      <c r="E8" s="40"/>
-      <c r="F8" s="40"/>
-      <c r="G8" s="41"/>
+      <c r="C8" s="42"/>
+      <c r="D8" s="43"/>
+      <c r="E8" s="43"/>
+      <c r="F8" s="43"/>
+      <c r="G8" s="44"/>
       <c r="L8" s="24" t="s">
         <v>20</v>
       </c>
@@ -1730,25 +1737,25 @@
       <c r="O8" s="24">
         <v>82</v>
       </c>
-      <c r="P8" s="64" t="b">
+      <c r="P8" s="37" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="Q8" s="64" t="b">
+      <c r="Q8" s="37" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="R8" s="63" t="b">
+      <c r="R8" s="24" t="b">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:28" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C9" s="39"/>
-      <c r="D9" s="40"/>
-      <c r="E9" s="40"/>
-      <c r="F9" s="40"/>
-      <c r="G9" s="41"/>
+      <c r="C9" s="42"/>
+      <c r="D9" s="43"/>
+      <c r="E9" s="43"/>
+      <c r="F9" s="43"/>
+      <c r="G9" s="44"/>
       <c r="L9" s="24" t="s">
         <v>21</v>
       </c>
@@ -1761,33 +1768,33 @@
       <c r="O9" s="24">
         <v>30</v>
       </c>
-      <c r="P9" s="63" t="b">
+      <c r="P9" s="24" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Q9" s="63" t="b">
+      <c r="Q9" s="24" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="R9" s="64" t="b">
+      <c r="R9" s="37" t="b">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:28" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C10" s="39"/>
-      <c r="D10" s="40"/>
-      <c r="E10" s="40"/>
-      <c r="F10" s="40"/>
-      <c r="G10" s="41"/>
+      <c r="C10" s="42"/>
+      <c r="D10" s="43"/>
+      <c r="E10" s="43"/>
+      <c r="F10" s="43"/>
+      <c r="G10" s="44"/>
     </row>
     <row r="11" spans="1:28" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B11" s="5"/>
-      <c r="C11" s="42"/>
-      <c r="D11" s="43"/>
-      <c r="E11" s="43"/>
-      <c r="F11" s="43"/>
-      <c r="G11" s="44"/>
+      <c r="C11" s="45"/>
+      <c r="D11" s="46"/>
+      <c r="E11" s="46"/>
+      <c r="F11" s="46"/>
+      <c r="G11" s="47"/>
     </row>
     <row r="12" spans="1:28" ht="15" customHeight="1" x14ac:dyDescent="0.5">
       <c r="B12" s="4"/>
@@ -1798,64 +1805,64 @@
     </row>
     <row r="14" spans="1:28" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B14" s="5"/>
-      <c r="C14" s="45" t="s">
+      <c r="C14" s="48" t="s">
         <v>5</v>
       </c>
-      <c r="D14" s="46"/>
-      <c r="E14" s="46"/>
-      <c r="F14" s="46"/>
-      <c r="G14" s="47"/>
+      <c r="D14" s="49"/>
+      <c r="E14" s="49"/>
+      <c r="F14" s="49"/>
+      <c r="G14" s="50"/>
     </row>
     <row r="15" spans="1:28" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B15" s="6"/>
-      <c r="C15" s="48"/>
-      <c r="D15" s="49"/>
-      <c r="E15" s="49"/>
-      <c r="F15" s="49"/>
-      <c r="G15" s="50"/>
+      <c r="C15" s="51"/>
+      <c r="D15" s="52"/>
+      <c r="E15" s="52"/>
+      <c r="F15" s="52"/>
+      <c r="G15" s="53"/>
     </row>
     <row r="16" spans="1:28" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B16" s="6"/>
-      <c r="C16" s="48"/>
-      <c r="D16" s="49"/>
-      <c r="E16" s="49"/>
-      <c r="F16" s="49"/>
-      <c r="G16" s="50"/>
+      <c r="C16" s="51"/>
+      <c r="D16" s="52"/>
+      <c r="E16" s="52"/>
+      <c r="F16" s="52"/>
+      <c r="G16" s="53"/>
     </row>
     <row r="17" spans="3:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C17" s="48"/>
-      <c r="D17" s="49"/>
-      <c r="E17" s="49"/>
-      <c r="F17" s="49"/>
-      <c r="G17" s="50"/>
+      <c r="C17" s="51"/>
+      <c r="D17" s="52"/>
+      <c r="E17" s="52"/>
+      <c r="F17" s="52"/>
+      <c r="G17" s="53"/>
     </row>
     <row r="18" spans="3:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C18" s="48"/>
-      <c r="D18" s="49"/>
-      <c r="E18" s="49"/>
-      <c r="F18" s="49"/>
-      <c r="G18" s="50"/>
+      <c r="C18" s="51"/>
+      <c r="D18" s="52"/>
+      <c r="E18" s="52"/>
+      <c r="F18" s="52"/>
+      <c r="G18" s="53"/>
     </row>
     <row r="19" spans="3:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C19" s="48"/>
-      <c r="D19" s="49"/>
-      <c r="E19" s="49"/>
-      <c r="F19" s="49"/>
-      <c r="G19" s="50"/>
+      <c r="C19" s="51"/>
+      <c r="D19" s="52"/>
+      <c r="E19" s="52"/>
+      <c r="F19" s="52"/>
+      <c r="G19" s="53"/>
     </row>
     <row r="20" spans="3:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C20" s="48"/>
-      <c r="D20" s="49"/>
-      <c r="E20" s="49"/>
-      <c r="F20" s="49"/>
-      <c r="G20" s="50"/>
+      <c r="C20" s="51"/>
+      <c r="D20" s="52"/>
+      <c r="E20" s="52"/>
+      <c r="F20" s="52"/>
+      <c r="G20" s="53"/>
     </row>
     <row r="21" spans="3:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C21" s="51"/>
-      <c r="D21" s="52"/>
-      <c r="E21" s="52"/>
-      <c r="F21" s="52"/>
-      <c r="G21" s="53"/>
+      <c r="C21" s="54"/>
+      <c r="D21" s="55"/>
+      <c r="E21" s="55"/>
+      <c r="F21" s="55"/>
+      <c r="G21" s="56"/>
     </row>
   </sheetData>
   <mergeCells count="11">
@@ -1911,23 +1918,23 @@
       <c r="H1" s="2"/>
       <c r="I1" s="8"/>
       <c r="J1" s="16"/>
-      <c r="K1" s="35" t="s">
+      <c r="K1" s="38" t="s">
         <v>0</v>
       </c>
-      <c r="L1" s="35"/>
+      <c r="L1" s="38"/>
       <c r="M1" s="15"/>
-      <c r="N1" s="35"/>
-      <c r="O1" s="35"/>
-      <c r="P1" s="35"/>
-      <c r="Q1" s="35"/>
-      <c r="R1" s="35"/>
-      <c r="S1" s="35"/>
-      <c r="T1" s="35"/>
-      <c r="U1" s="35"/>
-      <c r="V1" s="35"/>
-      <c r="W1" s="35"/>
-      <c r="X1" s="35"/>
-      <c r="Y1" s="35"/>
+      <c r="N1" s="38"/>
+      <c r="O1" s="38"/>
+      <c r="P1" s="38"/>
+      <c r="Q1" s="38"/>
+      <c r="R1" s="38"/>
+      <c r="S1" s="38"/>
+      <c r="T1" s="38"/>
+      <c r="U1" s="38"/>
+      <c r="V1" s="38"/>
+      <c r="W1" s="38"/>
+      <c r="X1" s="38"/>
+      <c r="Y1" s="38"/>
       <c r="Z1" s="15"/>
     </row>
     <row r="2" spans="1:26" ht="15" hidden="1" customHeight="1" thickTop="1" x14ac:dyDescent="0.3"/>
@@ -1945,13 +1952,13 @@
     </row>
     <row r="4" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="14"/>
-      <c r="C4" s="54" t="s">
+      <c r="C4" s="57" t="s">
         <v>8</v>
       </c>
-      <c r="D4" s="55"/>
-      <c r="E4" s="55"/>
-      <c r="F4" s="55"/>
-      <c r="G4" s="56"/>
+      <c r="D4" s="58"/>
+      <c r="E4" s="58"/>
+      <c r="F4" s="58"/>
+      <c r="G4" s="59"/>
       <c r="H4" s="14"/>
       <c r="I4" s="10"/>
       <c r="J4" s="18"/>
@@ -1980,11 +1987,11 @@
     </row>
     <row r="5" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="3"/>
-      <c r="C5" s="57"/>
-      <c r="D5" s="58"/>
-      <c r="E5" s="58"/>
-      <c r="F5" s="58"/>
-      <c r="G5" s="59"/>
+      <c r="C5" s="60"/>
+      <c r="D5" s="61"/>
+      <c r="E5" s="61"/>
+      <c r="F5" s="61"/>
+      <c r="G5" s="62"/>
       <c r="H5" s="3"/>
       <c r="I5" s="11"/>
       <c r="J5" s="19"/>
@@ -2006,17 +2013,17 @@
         <v>A</v>
       </c>
       <c r="Q5" s="22" t="str">
-        <f>IF(N5&gt;=85,"A",IF(N5&gt;=60,"B","C"))</f>
+        <f>IF(N5&gt;=85,"A",IF(N5&lt;60,"C","B"))</f>
         <v>B</v>
       </c>
       <c r="R5" s="22"/>
     </row>
     <row r="6" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C6" s="57"/>
-      <c r="D6" s="58"/>
-      <c r="E6" s="58"/>
-      <c r="F6" s="58"/>
-      <c r="G6" s="59"/>
+      <c r="C6" s="60"/>
+      <c r="D6" s="61"/>
+      <c r="E6" s="61"/>
+      <c r="F6" s="61"/>
+      <c r="G6" s="62"/>
       <c r="L6" s="24" t="s">
         <v>18</v>
       </c>
@@ -2034,17 +2041,17 @@
         <v>B</v>
       </c>
       <c r="Q6" s="22" t="str">
-        <f>IF(N6&gt;=85,"A",IF(N6&lt;60,"C","B"))</f>
+        <f t="shared" ref="Q6:Q9" si="1">IF(N6&gt;=85,"A",IF(N6&lt;60,"C","B"))</f>
         <v>C</v>
       </c>
       <c r="R6" s="22"/>
     </row>
     <row r="7" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C7" s="57"/>
-      <c r="D7" s="58"/>
-      <c r="E7" s="58"/>
-      <c r="F7" s="58"/>
-      <c r="G7" s="59"/>
+      <c r="C7" s="60"/>
+      <c r="D7" s="61"/>
+      <c r="E7" s="61"/>
+      <c r="F7" s="61"/>
+      <c r="G7" s="62"/>
       <c r="L7" s="24" t="s">
         <v>19</v>
       </c>
@@ -2062,17 +2069,17 @@
         <v>A</v>
       </c>
       <c r="Q7" s="22" t="str">
-        <f t="shared" ref="Q7:Q9" si="1">IF(N7&gt;=85,"A",IF(N7&lt;60,"C","B"))</f>
+        <f t="shared" si="1"/>
         <v>B</v>
       </c>
       <c r="R7" s="22"/>
     </row>
     <row r="8" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C8" s="57"/>
-      <c r="D8" s="58"/>
-      <c r="E8" s="58"/>
-      <c r="F8" s="58"/>
-      <c r="G8" s="59"/>
+      <c r="C8" s="60"/>
+      <c r="D8" s="61"/>
+      <c r="E8" s="61"/>
+      <c r="F8" s="61"/>
+      <c r="G8" s="62"/>
       <c r="L8" s="24" t="s">
         <v>20</v>
       </c>
@@ -2096,11 +2103,11 @@
       <c r="R8" s="22"/>
     </row>
     <row r="9" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C9" s="57"/>
-      <c r="D9" s="58"/>
-      <c r="E9" s="58"/>
-      <c r="F9" s="58"/>
-      <c r="G9" s="59"/>
+      <c r="C9" s="60"/>
+      <c r="D9" s="61"/>
+      <c r="E9" s="61"/>
+      <c r="F9" s="61"/>
+      <c r="G9" s="62"/>
       <c r="L9" s="24" t="s">
         <v>21</v>
       </c>
@@ -2124,19 +2131,19 @@
       <c r="R9" s="22"/>
     </row>
     <row r="10" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C10" s="57"/>
-      <c r="D10" s="58"/>
-      <c r="E10" s="58"/>
-      <c r="F10" s="58"/>
-      <c r="G10" s="59"/>
+      <c r="C10" s="60"/>
+      <c r="D10" s="61"/>
+      <c r="E10" s="61"/>
+      <c r="F10" s="61"/>
+      <c r="G10" s="62"/>
     </row>
     <row r="11" spans="1:26" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B11" s="5"/>
-      <c r="C11" s="60"/>
-      <c r="D11" s="61"/>
-      <c r="E11" s="61"/>
-      <c r="F11" s="61"/>
-      <c r="G11" s="62"/>
+      <c r="C11" s="63"/>
+      <c r="D11" s="64"/>
+      <c r="E11" s="64"/>
+      <c r="F11" s="64"/>
+      <c r="G11" s="65"/>
     </row>
     <row r="12" spans="1:26" ht="38.25" customHeight="1" x14ac:dyDescent="0.5">
       <c r="B12" s="4"/>
@@ -2171,13 +2178,13 @@
     </row>
     <row r="14" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B14" s="5"/>
-      <c r="C14" s="45" t="s">
+      <c r="C14" s="48" t="s">
         <v>7</v>
       </c>
-      <c r="D14" s="46"/>
-      <c r="E14" s="46"/>
-      <c r="F14" s="46"/>
-      <c r="G14" s="47"/>
+      <c r="D14" s="49"/>
+      <c r="E14" s="49"/>
+      <c r="F14" s="49"/>
+      <c r="G14" s="50"/>
       <c r="L14" s="29" t="s">
         <v>17</v>
       </c>
@@ -2191,21 +2198,21 @@
         <v>85</v>
       </c>
       <c r="P14" s="29" t="str">
-        <f>IF(AND(M14&gt;75,N14&gt;75,O14&gt;75),"Passed with distinction"," ")</f>
-        <v>Passed with distinction</v>
+        <f>IF(AND(M14&gt;75,N14&gt;75,O14&gt;75),"Passed with Distinction","")</f>
+        <v>Passed with Distinction</v>
       </c>
       <c r="Q14" s="29" t="str">
-        <f>IF(OR(O14&lt;35,N14&lt;35,M14&lt;35),"Failed","Promoted to next class")</f>
-        <v>Promoted to next class</v>
+        <f>IF(OR(M14&lt;35,N14&lt;35,O14&lt;35),"Failed","Promoted to next class.")</f>
+        <v>Promoted to next class.</v>
       </c>
     </row>
     <row r="15" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B15" s="6"/>
-      <c r="C15" s="48"/>
-      <c r="D15" s="49"/>
-      <c r="E15" s="49"/>
-      <c r="F15" s="49"/>
-      <c r="G15" s="50"/>
+      <c r="C15" s="51"/>
+      <c r="D15" s="52"/>
+      <c r="E15" s="52"/>
+      <c r="F15" s="52"/>
+      <c r="G15" s="53"/>
       <c r="L15" s="29" t="s">
         <v>18</v>
       </c>
@@ -2219,18 +2226,21 @@
         <v>43</v>
       </c>
       <c r="P15" s="29" t="str">
-        <f t="shared" ref="P15:P18" si="2">IF(AND(M15&gt;75,N15&gt;75,O15&gt;75),"Passed with distinction"," ")</f>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="Q15" s="29"/>
+        <f t="shared" ref="P15:P18" si="2">IF(AND(M15&gt;75,N15&gt;75,O15&gt;75),"Passed with Distinction","")</f>
+        <v/>
+      </c>
+      <c r="Q15" s="29" t="str">
+        <f t="shared" ref="Q15:Q18" si="3">IF(OR(M15&lt;35,N15&lt;35,O15&lt;35),"Failed","Promoted to next class.")</f>
+        <v>Promoted to next class.</v>
+      </c>
     </row>
     <row r="16" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B16" s="6"/>
-      <c r="C16" s="48"/>
-      <c r="D16" s="49"/>
-      <c r="E16" s="49"/>
-      <c r="F16" s="49"/>
-      <c r="G16" s="50"/>
+      <c r="C16" s="51"/>
+      <c r="D16" s="52"/>
+      <c r="E16" s="52"/>
+      <c r="F16" s="52"/>
+      <c r="G16" s="53"/>
       <c r="L16" s="29" t="s">
         <v>19</v>
       </c>
@@ -2245,16 +2255,19 @@
       </c>
       <c r="P16" s="29" t="str">
         <f t="shared" si="2"/>
-        <v>Passed with distinction</v>
-      </c>
-      <c r="Q16" s="29"/>
+        <v>Passed with Distinction</v>
+      </c>
+      <c r="Q16" s="29" t="str">
+        <f t="shared" si="3"/>
+        <v>Promoted to next class.</v>
+      </c>
     </row>
     <row r="17" spans="3:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C17" s="48"/>
-      <c r="D17" s="49"/>
-      <c r="E17" s="49"/>
-      <c r="F17" s="49"/>
-      <c r="G17" s="50"/>
+      <c r="C17" s="51"/>
+      <c r="D17" s="52"/>
+      <c r="E17" s="52"/>
+      <c r="F17" s="52"/>
+      <c r="G17" s="53"/>
       <c r="L17" s="29" t="s">
         <v>20</v>
       </c>
@@ -2269,16 +2282,19 @@
       </c>
       <c r="P17" s="29" t="str">
         <f t="shared" si="2"/>
-        <v>Passed with distinction</v>
-      </c>
-      <c r="Q17" s="29"/>
+        <v>Passed with Distinction</v>
+      </c>
+      <c r="Q17" s="29" t="str">
+        <f t="shared" si="3"/>
+        <v>Promoted to next class.</v>
+      </c>
     </row>
     <row r="18" spans="3:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C18" s="48"/>
-      <c r="D18" s="49"/>
-      <c r="E18" s="49"/>
-      <c r="F18" s="49"/>
-      <c r="G18" s="50"/>
+      <c r="C18" s="51"/>
+      <c r="D18" s="52"/>
+      <c r="E18" s="52"/>
+      <c r="F18" s="52"/>
+      <c r="G18" s="53"/>
       <c r="L18" s="29" t="s">
         <v>21</v>
       </c>
@@ -2293,30 +2309,33 @@
       </c>
       <c r="P18" s="29" t="str">
         <f t="shared" si="2"/>
-        <v xml:space="preserve"> </v>
-      </c>
-      <c r="Q18" s="29"/>
+        <v/>
+      </c>
+      <c r="Q18" s="29" t="str">
+        <f t="shared" si="3"/>
+        <v>Failed</v>
+      </c>
     </row>
     <row r="19" spans="3:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C19" s="48"/>
-      <c r="D19" s="49"/>
-      <c r="E19" s="49"/>
-      <c r="F19" s="49"/>
-      <c r="G19" s="50"/>
+      <c r="C19" s="51"/>
+      <c r="D19" s="52"/>
+      <c r="E19" s="52"/>
+      <c r="F19" s="52"/>
+      <c r="G19" s="53"/>
     </row>
     <row r="20" spans="3:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C20" s="48"/>
-      <c r="D20" s="49"/>
-      <c r="E20" s="49"/>
-      <c r="F20" s="49"/>
-      <c r="G20" s="50"/>
+      <c r="C20" s="51"/>
+      <c r="D20" s="52"/>
+      <c r="E20" s="52"/>
+      <c r="F20" s="52"/>
+      <c r="G20" s="53"/>
     </row>
     <row r="21" spans="3:17" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C21" s="51"/>
-      <c r="D21" s="52"/>
-      <c r="E21" s="52"/>
-      <c r="F21" s="52"/>
-      <c r="G21" s="53"/>
+      <c r="C21" s="54"/>
+      <c r="D21" s="55"/>
+      <c r="E21" s="55"/>
+      <c r="F21" s="55"/>
+      <c r="G21" s="56"/>
     </row>
   </sheetData>
   <mergeCells count="9">
@@ -2370,24 +2389,24 @@
       <c r="H1" s="2"/>
       <c r="I1" s="8"/>
       <c r="J1" s="16"/>
-      <c r="K1" s="35" t="s">
+      <c r="K1" s="38" t="s">
         <v>0</v>
       </c>
-      <c r="L1" s="35"/>
-      <c r="M1" s="35"/>
-      <c r="N1" s="35"/>
-      <c r="O1" s="35"/>
-      <c r="P1" s="35"/>
-      <c r="Q1" s="35"/>
-      <c r="R1" s="35"/>
-      <c r="S1" s="35"/>
-      <c r="T1" s="35"/>
-      <c r="U1" s="35"/>
-      <c r="V1" s="35"/>
-      <c r="W1" s="35"/>
-      <c r="X1" s="35"/>
-      <c r="Y1" s="35"/>
-      <c r="Z1" s="35"/>
+      <c r="L1" s="38"/>
+      <c r="M1" s="38"/>
+      <c r="N1" s="38"/>
+      <c r="O1" s="38"/>
+      <c r="P1" s="38"/>
+      <c r="Q1" s="38"/>
+      <c r="R1" s="38"/>
+      <c r="S1" s="38"/>
+      <c r="T1" s="38"/>
+      <c r="U1" s="38"/>
+      <c r="V1" s="38"/>
+      <c r="W1" s="38"/>
+      <c r="X1" s="38"/>
+      <c r="Y1" s="38"/>
+      <c r="Z1" s="38"/>
       <c r="AA1" s="15"/>
     </row>
     <row r="2" spans="1:27" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.3"/>
@@ -2396,13 +2415,13 @@
     </row>
     <row r="4" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="14"/>
-      <c r="C4" s="54" t="s">
+      <c r="C4" s="57" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="55"/>
-      <c r="E4" s="55"/>
-      <c r="F4" s="55"/>
-      <c r="G4" s="56"/>
+      <c r="D4" s="58"/>
+      <c r="E4" s="58"/>
+      <c r="F4" s="58"/>
+      <c r="G4" s="59"/>
       <c r="H4" s="14"/>
       <c r="I4" s="10"/>
       <c r="J4" s="18"/>
@@ -2431,11 +2450,11 @@
     </row>
     <row r="5" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="3"/>
-      <c r="C5" s="57"/>
-      <c r="D5" s="58"/>
-      <c r="E5" s="58"/>
-      <c r="F5" s="58"/>
-      <c r="G5" s="59"/>
+      <c r="C5" s="60"/>
+      <c r="D5" s="61"/>
+      <c r="E5" s="61"/>
+      <c r="F5" s="61"/>
+      <c r="G5" s="62"/>
       <c r="H5" s="3"/>
       <c r="I5" s="11"/>
       <c r="J5" s="19"/>
@@ -2466,11 +2485,11 @@
       </c>
     </row>
     <row r="6" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C6" s="57"/>
-      <c r="D6" s="58"/>
-      <c r="E6" s="58"/>
-      <c r="F6" s="58"/>
-      <c r="G6" s="59"/>
+      <c r="C6" s="60"/>
+      <c r="D6" s="61"/>
+      <c r="E6" s="61"/>
+      <c r="F6" s="61"/>
+      <c r="G6" s="62"/>
       <c r="L6" s="24" t="s">
         <v>18</v>
       </c>
@@ -2497,11 +2516,11 @@
       </c>
     </row>
     <row r="7" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C7" s="57"/>
-      <c r="D7" s="58"/>
-      <c r="E7" s="58"/>
-      <c r="F7" s="58"/>
-      <c r="G7" s="59"/>
+      <c r="C7" s="60"/>
+      <c r="D7" s="61"/>
+      <c r="E7" s="61"/>
+      <c r="F7" s="61"/>
+      <c r="G7" s="62"/>
       <c r="L7" s="24" t="s">
         <v>19</v>
       </c>
@@ -2528,11 +2547,11 @@
       </c>
     </row>
     <row r="8" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C8" s="57"/>
-      <c r="D8" s="58"/>
-      <c r="E8" s="58"/>
-      <c r="F8" s="58"/>
-      <c r="G8" s="59"/>
+      <c r="C8" s="60"/>
+      <c r="D8" s="61"/>
+      <c r="E8" s="61"/>
+      <c r="F8" s="61"/>
+      <c r="G8" s="62"/>
       <c r="L8" s="24" t="s">
         <v>20</v>
       </c>
@@ -2559,11 +2578,11 @@
       </c>
     </row>
     <row r="9" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C9" s="57"/>
-      <c r="D9" s="58"/>
-      <c r="E9" s="58"/>
-      <c r="F9" s="58"/>
-      <c r="G9" s="59"/>
+      <c r="C9" s="60"/>
+      <c r="D9" s="61"/>
+      <c r="E9" s="61"/>
+      <c r="F9" s="61"/>
+      <c r="G9" s="62"/>
       <c r="L9" s="24" t="s">
         <v>21</v>
       </c>
@@ -2590,11 +2609,11 @@
       </c>
     </row>
     <row r="10" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C10" s="57"/>
-      <c r="D10" s="58"/>
-      <c r="E10" s="58"/>
-      <c r="F10" s="58"/>
-      <c r="G10" s="59"/>
+      <c r="C10" s="60"/>
+      <c r="D10" s="61"/>
+      <c r="E10" s="61"/>
+      <c r="F10" s="61"/>
+      <c r="G10" s="62"/>
       <c r="L10" s="24" t="s">
         <v>44</v>
       </c>
@@ -2622,11 +2641,11 @@
     </row>
     <row r="11" spans="1:27" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B11" s="5"/>
-      <c r="C11" s="60"/>
-      <c r="D11" s="61"/>
-      <c r="E11" s="61"/>
-      <c r="F11" s="61"/>
-      <c r="G11" s="62"/>
+      <c r="C11" s="63"/>
+      <c r="D11" s="64"/>
+      <c r="E11" s="64"/>
+      <c r="F11" s="64"/>
+      <c r="G11" s="65"/>
     </row>
     <row r="12" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.5">
       <c r="B12" s="4"/>
@@ -2640,13 +2659,13 @@
     </row>
     <row r="14" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B14" s="5"/>
-      <c r="C14" s="45" t="s">
+      <c r="C14" s="48" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="46"/>
-      <c r="E14" s="46"/>
-      <c r="F14" s="46"/>
-      <c r="G14" s="47"/>
+      <c r="D14" s="49"/>
+      <c r="E14" s="49"/>
+      <c r="F14" s="49"/>
+      <c r="G14" s="50"/>
       <c r="L14" s="28" t="s">
         <v>29</v>
       </c>
@@ -2662,50 +2681,50 @@
     </row>
     <row r="15" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B15" s="6"/>
-      <c r="C15" s="48"/>
-      <c r="D15" s="49"/>
-      <c r="E15" s="49"/>
-      <c r="F15" s="49"/>
-      <c r="G15" s="50"/>
+      <c r="C15" s="51"/>
+      <c r="D15" s="52"/>
+      <c r="E15" s="52"/>
+      <c r="F15" s="52"/>
+      <c r="G15" s="53"/>
       <c r="L15" s="22" t="s">
         <v>30</v>
       </c>
       <c r="M15" s="24">
-        <f>COUNTIF($P$5:$P$9,L15)</f>
-        <v>3</v>
+        <f>COUNTIF($P$5:$P$10,L15)</f>
+        <v>4</v>
       </c>
       <c r="N15" s="24">
-        <f>COUNTIF($Q$5:$Q$9,L15)</f>
-        <v>1</v>
+        <f>COUNTIF($Q$5:$Q$10,L15)</f>
+        <v>2</v>
       </c>
       <c r="O15" s="24"/>
     </row>
     <row r="16" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B16" s="6"/>
-      <c r="C16" s="48"/>
-      <c r="D16" s="49"/>
-      <c r="E16" s="49"/>
-      <c r="F16" s="49"/>
-      <c r="G16" s="50"/>
+      <c r="C16" s="51"/>
+      <c r="D16" s="52"/>
+      <c r="E16" s="52"/>
+      <c r="F16" s="52"/>
+      <c r="G16" s="53"/>
       <c r="L16" s="22" t="s">
         <v>31</v>
       </c>
       <c r="M16" s="24">
-        <f t="shared" ref="M16:M17" si="6">COUNTIF($P$5:$P$9,L16)</f>
+        <f t="shared" ref="M16:M17" si="6">COUNTIF($P$5:$P$10,L16)</f>
         <v>2</v>
       </c>
       <c r="N16" s="24">
-        <f t="shared" ref="N16:N17" si="7">COUNTIF($Q$5:$Q$9,L16)</f>
+        <f>COUNTIF($Q$5:$Q$10,L16)</f>
         <v>3</v>
       </c>
       <c r="O16" s="24"/>
     </row>
     <row r="17" spans="3:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C17" s="48"/>
-      <c r="D17" s="49"/>
-      <c r="E17" s="49"/>
-      <c r="F17" s="49"/>
-      <c r="G17" s="50"/>
+      <c r="C17" s="51"/>
+      <c r="D17" s="52"/>
+      <c r="E17" s="52"/>
+      <c r="F17" s="52"/>
+      <c r="G17" s="53"/>
       <c r="L17" s="22" t="s">
         <v>32</v>
       </c>
@@ -2714,42 +2733,42 @@
         <v>0</v>
       </c>
       <c r="N17" s="24">
-        <f t="shared" si="7"/>
+        <f>COUNTIF($Q$5:$Q$10,L17)</f>
         <v>1</v>
       </c>
       <c r="O17" s="24"/>
     </row>
     <row r="18" spans="3:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C18" s="48"/>
-      <c r="D18" s="49"/>
-      <c r="E18" s="49"/>
-      <c r="F18" s="49"/>
-      <c r="G18" s="50"/>
+      <c r="C18" s="51"/>
+      <c r="D18" s="52"/>
+      <c r="E18" s="52"/>
+      <c r="F18" s="52"/>
+      <c r="G18" s="53"/>
     </row>
     <row r="19" spans="3:15" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C19" s="48"/>
-      <c r="D19" s="49"/>
-      <c r="E19" s="49"/>
-      <c r="F19" s="49"/>
-      <c r="G19" s="50"/>
+      <c r="C19" s="51"/>
+      <c r="D19" s="52"/>
+      <c r="E19" s="52"/>
+      <c r="F19" s="52"/>
+      <c r="G19" s="53"/>
       <c r="L19" s="26" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="20" spans="3:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C20" s="48"/>
-      <c r="D20" s="49"/>
-      <c r="E20" s="49"/>
-      <c r="F20" s="49"/>
-      <c r="G20" s="50"/>
+      <c r="C20" s="51"/>
+      <c r="D20" s="52"/>
+      <c r="E20" s="52"/>
+      <c r="F20" s="52"/>
+      <c r="G20" s="53"/>
       <c r="L20" s="30"/>
     </row>
     <row r="21" spans="3:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C21" s="51"/>
-      <c r="D21" s="52"/>
-      <c r="E21" s="52"/>
-      <c r="F21" s="52"/>
-      <c r="G21" s="53"/>
+      <c r="C21" s="54"/>
+      <c r="D21" s="55"/>
+      <c r="E21" s="55"/>
+      <c r="F21" s="55"/>
+      <c r="G21" s="56"/>
       <c r="L21" s="31" t="s">
         <v>39</v>
       </c>
@@ -2759,8 +2778,8 @@
         <v>37</v>
       </c>
       <c r="M22" s="20">
-        <f>COUNTIFS(M5:M9,L22,N5:N9,L22,O5:O9,L22)</f>
-        <v>0</v>
+        <f>COUNTIFS(M5:M10,L22,N5:N10,L22,O5:O10,L22)</f>
+        <v>1</v>
       </c>
       <c r="N22">
         <f>COUNTIFS(M5:M10,L22,N5:N10,L22,O5:O10,L22)</f>
@@ -2817,23 +2836,23 @@
       <c r="H1" s="2"/>
       <c r="I1" s="8"/>
       <c r="J1" s="16"/>
-      <c r="K1" s="35" t="s">
+      <c r="K1" s="38" t="s">
         <v>0</v>
       </c>
-      <c r="L1" s="35"/>
-      <c r="M1" s="35"/>
-      <c r="N1" s="35"/>
+      <c r="L1" s="38"/>
+      <c r="M1" s="38"/>
+      <c r="N1" s="38"/>
       <c r="O1" s="15"/>
-      <c r="P1" s="35"/>
-      <c r="Q1" s="35"/>
-      <c r="R1" s="35"/>
-      <c r="S1" s="35"/>
-      <c r="T1" s="35"/>
-      <c r="U1" s="35"/>
-      <c r="V1" s="35"/>
-      <c r="W1" s="35"/>
-      <c r="X1" s="35"/>
-      <c r="Y1" s="35"/>
+      <c r="P1" s="38"/>
+      <c r="Q1" s="38"/>
+      <c r="R1" s="38"/>
+      <c r="S1" s="38"/>
+      <c r="T1" s="38"/>
+      <c r="U1" s="38"/>
+      <c r="V1" s="38"/>
+      <c r="W1" s="38"/>
+      <c r="X1" s="38"/>
+      <c r="Y1" s="38"/>
       <c r="Z1" s="15"/>
     </row>
     <row r="2" spans="1:26" ht="15" customHeight="1" thickTop="1" x14ac:dyDescent="0.3"/>
@@ -2842,13 +2861,13 @@
     </row>
     <row r="4" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="14"/>
-      <c r="C4" s="54" t="s">
+      <c r="C4" s="57" t="s">
         <v>12</v>
       </c>
-      <c r="D4" s="55"/>
-      <c r="E4" s="55"/>
-      <c r="F4" s="55"/>
-      <c r="G4" s="56"/>
+      <c r="D4" s="58"/>
+      <c r="E4" s="58"/>
+      <c r="F4" s="58"/>
+      <c r="G4" s="59"/>
       <c r="H4" s="14"/>
       <c r="I4" s="10"/>
       <c r="J4" s="18"/>
@@ -2877,11 +2896,11 @@
     </row>
     <row r="5" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="3"/>
-      <c r="C5" s="57"/>
-      <c r="D5" s="58"/>
-      <c r="E5" s="58"/>
-      <c r="F5" s="58"/>
-      <c r="G5" s="59"/>
+      <c r="C5" s="60"/>
+      <c r="D5" s="61"/>
+      <c r="E5" s="61"/>
+      <c r="F5" s="61"/>
+      <c r="G5" s="62"/>
       <c r="H5" s="3"/>
       <c r="I5" s="11"/>
       <c r="J5" s="19"/>
@@ -2912,11 +2931,11 @@
       </c>
     </row>
     <row r="6" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C6" s="57"/>
-      <c r="D6" s="58"/>
-      <c r="E6" s="58"/>
-      <c r="F6" s="58"/>
-      <c r="G6" s="59"/>
+      <c r="C6" s="60"/>
+      <c r="D6" s="61"/>
+      <c r="E6" s="61"/>
+      <c r="F6" s="61"/>
+      <c r="G6" s="62"/>
       <c r="L6" s="20" t="s">
         <v>18</v>
       </c>
@@ -2943,11 +2962,11 @@
       </c>
     </row>
     <row r="7" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C7" s="57"/>
-      <c r="D7" s="58"/>
-      <c r="E7" s="58"/>
-      <c r="F7" s="58"/>
-      <c r="G7" s="59"/>
+      <c r="C7" s="60"/>
+      <c r="D7" s="61"/>
+      <c r="E7" s="61"/>
+      <c r="F7" s="61"/>
+      <c r="G7" s="62"/>
       <c r="L7" s="20" t="s">
         <v>19</v>
       </c>
@@ -2974,11 +2993,11 @@
       </c>
     </row>
     <row r="8" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C8" s="57"/>
-      <c r="D8" s="58"/>
-      <c r="E8" s="58"/>
-      <c r="F8" s="58"/>
-      <c r="G8" s="59"/>
+      <c r="C8" s="60"/>
+      <c r="D8" s="61"/>
+      <c r="E8" s="61"/>
+      <c r="F8" s="61"/>
+      <c r="G8" s="62"/>
       <c r="L8" s="20" t="s">
         <v>20</v>
       </c>
@@ -3005,11 +3024,11 @@
       </c>
     </row>
     <row r="9" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C9" s="57"/>
-      <c r="D9" s="58"/>
-      <c r="E9" s="58"/>
-      <c r="F9" s="58"/>
-      <c r="G9" s="59"/>
+      <c r="C9" s="60"/>
+      <c r="D9" s="61"/>
+      <c r="E9" s="61"/>
+      <c r="F9" s="61"/>
+      <c r="G9" s="62"/>
       <c r="L9" s="20" t="s">
         <v>21</v>
       </c>
@@ -3019,7 +3038,7 @@
       <c r="N9" s="20">
         <v>60</v>
       </c>
-      <c r="O9" s="66">
+      <c r="O9" s="36">
         <v>30</v>
       </c>
       <c r="P9" s="20" t="b">
@@ -3036,19 +3055,19 @@
       </c>
     </row>
     <row r="10" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C10" s="57"/>
-      <c r="D10" s="58"/>
-      <c r="E10" s="58"/>
-      <c r="F10" s="58"/>
-      <c r="G10" s="59"/>
+      <c r="C10" s="60"/>
+      <c r="D10" s="61"/>
+      <c r="E10" s="61"/>
+      <c r="F10" s="61"/>
+      <c r="G10" s="62"/>
     </row>
     <row r="11" spans="1:26" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B11" s="5"/>
-      <c r="C11" s="60"/>
-      <c r="D11" s="61"/>
-      <c r="E11" s="61"/>
-      <c r="F11" s="61"/>
-      <c r="G11" s="62"/>
+      <c r="C11" s="63"/>
+      <c r="D11" s="64"/>
+      <c r="E11" s="64"/>
+      <c r="F11" s="64"/>
+      <c r="G11" s="65"/>
       <c r="L11" s="26" t="s">
         <v>41</v>
       </c>
@@ -3075,13 +3094,13 @@
     </row>
     <row r="14" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B14" s="5"/>
-      <c r="C14" s="45" t="s">
+      <c r="C14" s="48" t="s">
         <v>11</v>
       </c>
-      <c r="D14" s="46"/>
-      <c r="E14" s="46"/>
-      <c r="F14" s="46"/>
-      <c r="G14" s="47"/>
+      <c r="D14" s="49"/>
+      <c r="E14" s="49"/>
+      <c r="F14" s="49"/>
+      <c r="G14" s="50"/>
       <c r="L14" s="21" t="b">
         <v>0</v>
       </c>
@@ -3100,54 +3119,54 @@
     </row>
     <row r="15" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B15" s="6"/>
-      <c r="C15" s="48"/>
-      <c r="D15" s="49"/>
-      <c r="E15" s="49"/>
-      <c r="F15" s="49"/>
-      <c r="G15" s="50"/>
+      <c r="C15" s="51"/>
+      <c r="D15" s="52"/>
+      <c r="E15" s="52"/>
+      <c r="F15" s="52"/>
+      <c r="G15" s="53"/>
     </row>
     <row r="16" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B16" s="6"/>
-      <c r="C16" s="48"/>
-      <c r="D16" s="49"/>
-      <c r="E16" s="49"/>
-      <c r="F16" s="49"/>
-      <c r="G16" s="50"/>
+      <c r="C16" s="51"/>
+      <c r="D16" s="52"/>
+      <c r="E16" s="52"/>
+      <c r="F16" s="52"/>
+      <c r="G16" s="53"/>
     </row>
     <row r="17" spans="3:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C17" s="48"/>
-      <c r="D17" s="49"/>
-      <c r="E17" s="49"/>
-      <c r="F17" s="49"/>
-      <c r="G17" s="50"/>
+      <c r="C17" s="51"/>
+      <c r="D17" s="52"/>
+      <c r="E17" s="52"/>
+      <c r="F17" s="52"/>
+      <c r="G17" s="53"/>
     </row>
     <row r="18" spans="3:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C18" s="48"/>
-      <c r="D18" s="49"/>
-      <c r="E18" s="49"/>
-      <c r="F18" s="49"/>
-      <c r="G18" s="50"/>
+      <c r="C18" s="51"/>
+      <c r="D18" s="52"/>
+      <c r="E18" s="52"/>
+      <c r="F18" s="52"/>
+      <c r="G18" s="53"/>
     </row>
     <row r="19" spans="3:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C19" s="48"/>
-      <c r="D19" s="49"/>
-      <c r="E19" s="49"/>
-      <c r="F19" s="49"/>
-      <c r="G19" s="50"/>
+      <c r="C19" s="51"/>
+      <c r="D19" s="52"/>
+      <c r="E19" s="52"/>
+      <c r="F19" s="52"/>
+      <c r="G19" s="53"/>
     </row>
     <row r="20" spans="3:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C20" s="48"/>
-      <c r="D20" s="49"/>
-      <c r="E20" s="49"/>
-      <c r="F20" s="49"/>
-      <c r="G20" s="50"/>
+      <c r="C20" s="51"/>
+      <c r="D20" s="52"/>
+      <c r="E20" s="52"/>
+      <c r="F20" s="52"/>
+      <c r="G20" s="53"/>
     </row>
     <row r="21" spans="3:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C21" s="51"/>
-      <c r="D21" s="52"/>
-      <c r="E21" s="52"/>
-      <c r="F21" s="52"/>
-      <c r="G21" s="53"/>
+      <c r="C21" s="54"/>
+      <c r="D21" s="55"/>
+      <c r="E21" s="55"/>
+      <c r="F21" s="55"/>
+      <c r="G21" s="56"/>
     </row>
   </sheetData>
   <mergeCells count="9">
